--- a/data/dividends_info_20260927.xlsx
+++ b/data/dividends_info_20260927.xlsx
@@ -2095,7 +2095,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2112,7 +2112,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2129,7 +2129,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2146,7 +2146,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2180,7 +2180,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2197,7 +2197,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2214,7 +2214,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>JUVENTUS F.C. S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2224,14 +2224,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2248,7 +2248,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2265,7 +2265,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2282,7 +2282,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2299,7 +2299,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2309,14 +2309,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2333,7 +2333,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2350,7 +2350,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2367,7 +2367,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2384,7 +2384,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2401,7 +2401,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2418,7 +2418,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2452,7 +2452,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2469,7 +2469,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2486,7 +2486,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2503,7 +2503,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Gens Aurea S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2571,7 +2571,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2588,7 +2588,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2615,14 +2615,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2639,7 +2639,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2656,7 +2656,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2673,7 +2673,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2690,7 +2690,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2724,7 +2724,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2741,7 +2741,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2758,7 +2758,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2775,7 +2775,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2809,7 +2809,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2826,7 +2826,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2843,7 +2843,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2860,7 +2860,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2877,7 +2877,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2904,14 +2904,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2928,7 +2928,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2945,7 +2945,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2962,7 +2962,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2979,7 +2979,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2996,7 +2996,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3013,7 +3013,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3030,7 +3030,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3040,14 +3040,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ETI S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3064,7 +3064,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EPH INVEST S.p.A.</t>
+          <t>ETI S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3081,7 +3081,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>EPH INVEST S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3098,7 +3098,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3108,14 +3108,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3125,14 +3125,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3149,7 +3149,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Dipietro Group S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3166,7 +3166,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3183,7 +3183,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3200,7 +3200,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>Dipietro Group S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3217,7 +3217,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3251,7 +3251,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3268,7 +3268,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3285,7 +3285,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3319,7 +3319,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3353,7 +3353,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3370,7 +3370,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3387,7 +3387,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3404,7 +3404,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>OPT S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3421,7 +3421,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3431,14 +3431,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3455,7 +3455,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>OPT S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3472,7 +3472,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3489,7 +3489,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3499,14 +3499,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3523,7 +3523,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3540,7 +3540,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3557,7 +3557,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3574,7 +3574,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3584,14 +3584,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3608,7 +3608,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3625,7 +3625,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3642,7 +3642,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3659,7 +3659,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3676,7 +3676,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3693,7 +3693,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3710,7 +3710,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3727,7 +3727,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3744,7 +3744,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3754,14 +3754,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3771,14 +3771,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3795,7 +3795,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3812,7 +3812,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3822,14 +3822,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3846,7 +3846,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3863,7 +3863,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3880,7 +3880,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Alia Mentis S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3897,7 +3897,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3914,7 +3914,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3931,7 +3931,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3948,7 +3948,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3965,7 +3965,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3982,7 +3982,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3999,7 +3999,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4016,7 +4016,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4026,14 +4026,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>First Point S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4050,7 +4050,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4084,7 +4084,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4101,7 +4101,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>First Point S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4135,7 +4135,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4152,7 +4152,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4169,7 +4169,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4186,7 +4186,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4203,7 +4203,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4213,14 +4213,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4237,7 +4237,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4254,7 +4254,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4271,7 +4271,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Alia Mentis S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4288,7 +4288,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4305,7 +4305,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4315,14 +4315,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>SB Annual Report</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4339,7 +4339,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4356,7 +4356,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>LANDI RENZO S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4366,14 +4366,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>LANDI RENZO S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4383,14 +4383,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>SB Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4485,14 +4485,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4526,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4536,14 +4536,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4560,7 +4560,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4570,14 +4570,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -4645,7 +4645,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4655,14 +4655,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4679,7 +4679,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4706,14 +4706,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4740,14 +4740,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4757,14 +4757,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4859,14 +4859,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4876,14 +4876,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4893,14 +4893,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4910,14 +4910,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4934,7 +4934,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4951,7 +4951,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -4968,7 +4968,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5002,7 +5002,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5019,7 +5019,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5036,7 +5036,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5070,7 +5070,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5080,14 +5080,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5097,14 +5097,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>LANDI RENZO S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5172,7 +5172,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>LANDI RENZO S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -5206,7 +5206,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5223,7 +5223,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5257,7 +5257,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5267,14 +5267,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5312,112 +5312,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DIGITAL BROS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ferretti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>MAIRE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>MAIRE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>eVISO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>